--- a/恒生银信招标资讯每日速递_2026年7月17日.xlsx
+++ b/恒生银信招标资讯每日速递_2026年7月17日.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部有效招标（51）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="银行行业（35）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部有效招标（53）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="银行行业（37）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信托行业（16）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强烈建议投标（9）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建议投标（24）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强烈建议投标（10）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建议投标（25）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1914,57 +1914,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>江苏银行</t>
+          <t>青银理财</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-2027年基金指数和市场情绪数据采购</t>
+          <t>财务管理系统二期项目</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>为满足业务发展的需要，拟采购基金指数和市场情绪数据服务，用于专业投资研究建设。包括但不限于指数专区、FOF专区、全球市场专区、正收益排行榜、定制化投研、超级指标、纯债基金等基金专区等。本项目2026-07-03首次招标，07-13终止后于当日重新发布招标公告。</t>
+          <t>财务管理系统二期建设。邀请采购，受邀供应商为用友金融信息技术股份有限公司，答复截止2026-07-27，07-28竞价。</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 09:00</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>邀请招标</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>李智龙 13952002026；代理机构：江苏省招标中心有限公司 025-83301084</t>
+          <t>青银理财 0532-66723897（青岛阳光采购平台）</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>数据服务、金融市场/资金/同业</t>
+          <t>数据平台</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>☆☆☆ 不建议</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>银行旧关键词</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -1984,27 +1984,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>农行江苏分行</t>
+          <t>江苏银行</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>智能资产配置服务项目</t>
+          <t>2026-2027年基金指数和市场情绪数据采购</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>为进一步加快财富管理业务发展，为基层理财经理及财富顾问提供专业支持，全面提升私行及高价值客户服务效率，拟采购智能资产配置服务。通过引入外部权威数据及模型规则，推动AI赋能智能化配置，提升服务效率和财富管理专业化水平。实施周期3个月，服务期12个月。</t>
+          <t>为满足业务发展的需要，拟采购基金指数和市场情绪数据服务，用于专业投资研究建设。包括但不限于指数专区、FOF专区、全球市场专区、正收益排行榜、定制化投研、超级指标、纯债基金等基金专区等。本项目2026-07-03首次招标，07-13终止后于当日重新发布招标公告。</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>424.5万元（不含税）</t>
+          <t>71万元</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23 09:00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>招标编号：JSTCC26005104585；代理机构：江苏省招标中心有限公司</t>
+          <t>李智龙 13952002026；代理机构：江苏省招标中心有限公司 025-83301084</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>财富管理</t>
+          <t>数据服务、金融市场/资金/同业</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>银行旧关键词</t>
         </is>
       </c>
     </row>
@@ -2049,27 +2049,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>紫金信托</t>
+          <t>农行江苏分行</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>资产管理信托技术服务供应商资源池项目</t>
+          <t>智能资产配置服务项目</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>资产管理信托业务技术服务供应商资源池，为技术开发服务储备供应商，属人力外包类。</t>
+          <t>为进一步加快财富管理业务发展，为基层理财经理及财富顾问提供专业支持，全面提升私行及高价值客户服务效率，拟采购智能资产配置服务。通过引入外部权威数据及模型规则，推动AI赋能智能化配置，提升服务效率和财富管理专业化水平。实施周期3个月，服务期12个月。</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>424.5万元（不含税）</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>代理机构：江苏省招标中心有限公司 刘欣楠、郭家栋 025-82281929</t>
+          <t>招标编号：JSTCC26005104585；代理机构：江苏省招标中心有限公司</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>人力外包、资产管理</t>
+          <t>财富管理</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -2114,27 +2114,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>苏州农商</t>
+          <t>紫金信托</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（人工智能）</t>
+          <t>资产管理信托技术服务供应商资源池项目</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>江苏苏州农商行数据类通用技术外包服务项目（人工智能方向），框架入围不超过10家供应商，协议期限3年。</t>
+          <t>资产管理信托业务技术服务供应商资源池，为技术开发服务储备供应商，属人力外包类。</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>框架入围（无固定总预算）</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:00</t>
+          <t>2026-08-05 09:30</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785；标书寄送地址：苏州市吴江区东太湖大道10888号（苏州农商银行综合大楼一楼收发室集采专用）</t>
+          <t>代理机构：江苏省招标中心有限公司 刘欣楠、郭家栋 025-82281929</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>人力外包、大模型应用</t>
+          <t>人力外包、资产管理</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 已截止</t>
+          <t>👀 ★☆☆ 可关注</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>苏州农商银行采购管理平台</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -2184,17 +2184,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（应用开发）</t>
+          <t>2026年度数据类通用技术外包服务项目（人工智能）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行数据类通用技术外包服务采购，提供应用开发技术外包服务，框架协议形式，入围供应商不超过15家，协议期限3年。</t>
+          <t>江苏苏州农商行数据类通用技术外包服务项目（人工智能方向），框架入围不超过10家供应商，协议期限3年。</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>框架待查</t>
+          <t>框架入围（无固定总预算）</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785；苏州市吴江区东太湖大道10888号苏州农商银行综合大楼一楼收发室集采专用</t>
+          <t>钱女士 0512-63969785；标书寄送地址：苏州市吴江区东太湖大道10888号（苏州农商银行综合大楼一楼收发室集采专用）</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>数据平台、人力外包</t>
+          <t>人力外包、大模型应用</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行官网</t>
+          <t>苏州农商银行采购管理平台</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（数据分析）</t>
+          <t>2026年度数据类通用技术外包服务项目（应用开发）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行数据类通用技术外包服务采购，提供数据分析技术外包服务，框架协议形式，入围供应商不超过10家，协议期限3年。</t>
+          <t>苏州农商行数据类通用技术外包服务采购，提供应用开发技术外包服务，框架协议形式，入围供应商不超过15家，协议期限3年。</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>数据服务、人力外包</t>
+          <t>数据平台、人力外包</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>数据类通用技术外包服务采购（数据开发）</t>
+          <t>2026年度数据类通用技术外包服务项目（数据分析）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>采购数据开发类通用技术外包服务，入围供应商不超过15家，签订3年期数据开发类通用技术外包框架合同。</t>
+          <t>苏州农商行数据类通用技术外包服务采购，提供数据分析技术外包服务，框架协议形式，入围供应商不超过10家，协议期限3年。</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>框架待查</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 23:59</t>
+          <t>2026-07-16 16:00</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785（入围15家，3年框架）</t>
+          <t>钱女士 0512-63969785；苏州市吴江区东太湖大道10888号苏州农商银行综合大楼一楼收发室集采专用</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>数据平台、人力外包</t>
+          <t>数据服务、人力外包</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>苏州农商银行采购管理平台</t>
+          <t>苏州农商行官网</t>
         </is>
       </c>
     </row>
@@ -2369,22 +2369,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>浙商银行</t>
+          <t>苏州农商</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>国产化资产托管系统建设及个性化功能迁移改造项目</t>
+          <t>数据类通用技术外包服务采购（数据开发）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>国产化资产托管系统建设及个性化功能迁移改造，需通过POC测试。竞争性磋商。磋商保证金：10万元。</t>
+          <t>采购数据开发类通用技术外包服务，入围供应商不超过15家，签订3年期数据开发类通用技术外包框架合同。</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 09:00</t>
+          <t>2026-07-16 23:59</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>竞争性磋商</t>
+          <t>公开招标</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>季老师 0571-88260758；POC测试联系人：程老师 0571-****1279</t>
+          <t>钱女士 0512-63969785（入围15家，3年框架）</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>信创/国产化、资产托管</t>
+          <t>数据平台、人力外包</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>☆☆☆ 已截止</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>苏州农商银行采购管理平台</t>
         </is>
       </c>
     </row>
@@ -2434,52 +2434,52 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>浙商银行</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>国产化资产托管系统建设及个性化功能迁移改造项目</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>国产化资产托管系统建设及个性化功能迁移改造，需通过POC测试。竞争性磋商。磋商保证金：10万元。</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-07-24 09:00</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>竞争性磋商</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>季老师 0571-88260758；POC测试联系人：程老师 0571-****1279</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>信创/国产化、资产托管</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>兴银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>理财登记过户（TA）系统产品优化项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>145.89万元</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:30</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2599,22 +2599,22 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -2629,32 +2629,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>兴业信托</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026年资管系统数据资讯服务项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>采购资管系统数据资讯服务，支持信托资产管理业务的数据需求，预算106万元。</t>
+          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>106万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27 13:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>联系方式：19*******37（需登录水滴标讯查看完整联系方式）</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据服务</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>水滴标讯</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -2689,37 +2689,37 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴银理财</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
+          <t>理财登记过户（TA）系统产品优化项目</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
+          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>145.89万元</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:30</t>
+          <t>2026-08-07 09:30</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
+          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>移动支付网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -2754,37 +2754,37 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴业信托</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+          <t>2026年资管系统数据资讯服务项目</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+          <t>采购资管系统数据资讯服务，支持信托资产管理业务的数据需求，预算106万元。</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>106万元</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-27 13:30</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2794,22 +2794,22 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+          <t>联系方式：19*******37（需登录水滴标讯查看完整联系方式）</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理、数据服务</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>水滴标讯</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-31 09:30</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>移动支付网</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2894,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>中原信托</t>
+          <t>中原银行</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>中原信托有限公司信创基础资源平台扩容建设项目</t>
+          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>中原信托信创基础资源平台扩容建设，分3个标段：一标段ARM服务器、二标段C86服务器、三标段基础硬件及软件。交货期30日历天。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 9:00</t>
+          <t>2026-07-31 14:30</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2924,22 +2924,22 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>招标人：王先生 0371-86230661 / 代理机构：李素一、何小宁 0371-65928022 / 邮箱 hnjdgf01@163.com</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>信创/国产化、数据平台</t>
+          <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>电力招标采购网</t>
         </is>
       </c>
     </row>
@@ -2954,32 +2954,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>湖南银行</t>
+          <t>中原银行</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026年数字人民币系统研发项目</t>
+          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>60万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 10:00</t>
+          <t>2026-07-31 14:30</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2989,22 +2989,22 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
+          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>渠道系统、信创/国产化</t>
+          <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>湖南银行官网</t>
+          <t>电力招标采购网</t>
         </is>
       </c>
     </row>
@@ -3019,32 +3019,32 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>湖南银行</t>
+          <t>中原信托</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>客户经理工作台（投顾版）建设项目</t>
+          <t>中原信托有限公司信创基础资源平台扩容建设项目</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
+          <t>中原信托信创基础资源平台扩容建设，分3个标段：一标段ARM服务器、二标段C86服务器、三标段基础硬件及软件。交货期30日历天。</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>220万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 23:59</t>
+          <t>2026-07-30 9:00</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3054,22 +3054,22 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
+          <t>招标人：王先生 0371-86230661 / 代理机构：李素一、何小宁 0371-65928022 / 邮箱 hnjdgf01@163.com</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>财富管理、渠道系统</t>
+          <t>信创/国产化、数据平台</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>👀 ★☆☆ 可关注</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>湖南招标网</t>
+          <t>中招联合</t>
         </is>
       </c>
     </row>
@@ -3079,37 +3079,37 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>四川农商联合银行</t>
+          <t>湖南银行</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>大模型基础平台及业务创新场景研发项目-智能算力资源采购</t>
+          <t>2026年数字人民币系统研发项目</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>采购智能算力服务器资源，用于大模型平台项目开发测试环境。</t>
+          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>439.2万元</t>
+          <t>60万元</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 11:00</t>
+          <t>2026-07-22 10:00</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3119,22 +3119,22 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>028-85357015</t>
+          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>渠道系统、信创/国产化</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>湖南银行官网</t>
         </is>
       </c>
     </row>
@@ -3144,52 +3144,52 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>华能贵诚信托</t>
+          <t>湖南银行</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>估值系统上交所新竞价新综业改造项目</t>
+          <t>客户经理工作台（投顾版）建设项目</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>恒生估值核算系统上交所新债券竞价、新综合业务平台相关改造。直接采购，拟定供应商为恒生电子股份有限公司，公示期2026-07-16至07-19。</t>
+          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>220万元</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-23 23:59</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>单一来源采购</t>
+          <t>公开招标</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>周经理 010-68292029 zhouys@hngtrust.com</t>
+          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>财富管理、渠道系统</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>湖南招标网</t>
         </is>
       </c>
     </row>
@@ -3214,32 +3214,32 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>贵州农商联合银行</t>
+          <t>四川农商联合银行</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>IT资产设备统一技术选型（国产PC终端、国产黑白A4打印机）</t>
+          <t>大模型基础平台及业务创新场景研发项目-智能算力资源采购</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>国产PC终端、国产黑白A4打印机技术选型</t>
+          <t>采购智能算力服务器资源，用于大模型平台项目开发测试环境。</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>439.2万元</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21 11:00</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>陈老师(业务)/代老师(招标) 18748826330/0851-82592720; 潘瑞/桂刚/钱大鹏/刘岳(代理) 0851-84812466</t>
+          <t>028-85357015</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>信创/国产化</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>贵州农商联合银行</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>反洗钱系统升级优化与维保服务项目</t>
+          <t>估值系统上交所新竞价新综业改造项目</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>反洗钱系统升级优化与维保。直接采购，拟定供应商为北京捷软世纪信息技术有限公司，公示期2026-07-15至07-18。</t>
+          <t>恒生估值核算系统上交所新债券竞价、新综合业务平台相关改造。直接采购，拟定供应商为恒生电子股份有限公司，公示期2026-07-16至07-19。</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>周经理 010-68292300</t>
+          <t>周经理 010-68292029 zhouys@hngtrust.com</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>风控合规、运维服务</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 不建议</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>华能贵诚信托</t>
+          <t>贵州农商联合银行</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>风控百融平台运维服务项目</t>
+          <t>IT资产设备统一技术选型（国产PC终端、国产黑白A4打印机）</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>风控百融平台运维服务。直接采购，拟定供应商为百融至信（北京）科技有限公司，公示期2026-07-15至07-18。</t>
+          <t>国产PC终端、国产黑白A4打印机技术选型</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3369,32 +3369,32 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>单一来源采购</t>
+          <t>公开招标</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>周经理 010-68292300</t>
+          <t>陈老师(业务)/代老师(招标) 18748826330/0851-82592720; 潘瑞/桂刚/钱大鹏/刘岳(代理) 0851-84812466</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>运维服务、风控合规</t>
+          <t>信创/国产化</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 不建议</t>
+          <t>👀 ★☆☆ 可关注</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>贵州农商联合银行</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>金证TA系统运维服务项目</t>
+          <t>反洗钱系统升级优化与维保服务项目</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>金证TA系统运维服务。直接采购，拟定供应商为金证科技股份有限公司，公示期2026-07-16至07-19。</t>
+          <t>反洗钱系统升级优化与维保。直接采购，拟定供应商为北京捷软世纪信息技术有限公司，公示期2026-07-15至07-18。</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>运维服务</t>
+          <t>风控合规、运维服务</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3474,57 +3474,57 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>建行云南分行</t>
+          <t>华能贵诚信托</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>云南省2026至2027年度信息技术开发服务</t>
+          <t>风控百融平台运维服务项目</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>云南建行特色业务应用系统研发，涵盖财政、社保、医保、ETC、资金监管、个人金融等业务系统的迭代优化、云原生及信创改造，提供软件开发技术人力服务。入选3家，配额5:3:2。</t>
+          <t>风控百融平台运维服务。直接采购，拟定供应商为百融至信（北京）科技有限公司，公示期2026-07-15至07-18。</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1237.2万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 09:30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>单一来源采购</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>李老师 0871-63063106 / 0871-63063110；代理机构：杨倩 15911660979 / 340551535@qq.com</t>
+          <t>周经理 010-68292300</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>人力外包、信创/国产化</t>
+          <t>运维服务、风控合规</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 已截止</t>
+          <t>☆☆☆ 不建议</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>建设银行龙集采平台</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -3534,27 +3534,27 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>华润信托</t>
+          <t>华能贵诚信托</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026年实时数据同步平台项目</t>
+          <t>金证TA系统运维服务项目</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>采购实时数据同步平台，含5条链路永久授权、部署实施及1年维保。原06-23公告已终止，07-15重新发布谈判采购公告（编号LX[2026]070002）。</t>
+          <t>金证TA系统运维服务。直接采购，拟定供应商为金证科技股份有限公司，公示期2026-07-16至07-19。</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3564,27 +3564,27 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 09:30</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>竞争性谈判</t>
+          <t>单一来源采购</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>吕启芳 13689561200 lvqf@crctrust.com</t>
+          <t>周经理 010-68292300</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>数据平台</t>
+          <t>运维服务</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>☆☆☆ 不建议</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3599,37 +3599,37 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>广州农商</t>
+          <t>建行云南分行</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>同业客户信息数据服务项目</t>
+          <t>云南省2026至2027年度信息技术开发服务</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>采购同业客户信息数据服务，包括监管报送数据（含同业客户基本信息）及风控数据（含诚信档案、司法诉讼、同业机构新闻舆情数据）等，项目限价118万元，采购有效期2年。</t>
+          <t>云南建行特色业务应用系统研发，涵盖财政、社保、医保、ETC、资金监管、个人金融等业务系统的迭代优化、云原生及信创改造，提供软件开发技术人力服务。入选3家，配额5:3:2。</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>118万元</t>
+          <t>1237.2万元</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 9:00</t>
+          <t>2026-07-16 09:30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>潘先生 020-22389241 / 邮箱 panchaoning@grcbank.com</t>
+          <t>李老师 0871-63063106 / 0871-63063110；代理机构：杨倩 15911660979 / 340551535@qq.com</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、数据服务、风控合规</t>
+          <t>人力外包、信创/国产化</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>☆☆☆ 已截止</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>广州农商银行官网</t>
+          <t>建设银行龙集采平台</t>
         </is>
       </c>
     </row>
@@ -3674,42 +3674,42 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>南粤银行</t>
+          <t>华润信托</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行新国际结算系统建设项目</t>
+          <t>2026年实时数据同步平台项目</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行新国际结算系统建设，预算260万元。要求投标人具有2021年1月1日以来独立承建国内商业银行（资产规模≥3000亿元）总行级别国际结算系统成功案例。</t>
+          <t>采购实时数据同步平台，含5条链路永久授权、部署实施及1年维保。原06-23公告已终止，07-15重新发布谈判采购公告（编号LX[2026]070002）。</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>260万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 10:00</t>
+          <t>2026-07-21 09:30</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>竞争性谈判</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>陈先生(招标人) 020-28870611; 潘工/祝工(代理) 020-87543323 3271382737@qq.com</t>
+          <t>吕启芳 13689561200 lvqf@crctrust.com</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、渠道系统</t>
+          <t>数据平台</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行官网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -3744,22 +3744,22 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026-2028年大模型协同计算平台人月外包开发服务</t>
+          <t>同业客户信息数据服务项目</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>为大模型协同计算平台HiAgent大模型智能体、智能数据洞察大模型、大模型方舟平台等产品的定制化开发，以及报告生成、知识库问答、智能问数及ArkClaw数字员工等智能体建设需求，提供人月外包开发服务。</t>
+          <t>采购同业客户信息数据服务，包括监管报送数据（含同业客户基本信息）及风控数据（含诚信档案、司法诉讼、同业机构新闻舆情数据）等，项目限价118万元，采购有效期2年。</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>92.16万元</t>
+          <t>118万元</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:00</t>
+          <t>2026-07-30 9:00</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>潘先生 020-22389241 / panchaoning@grcbank.com</t>
+          <t>潘先生 020-22389241 / 邮箱 panchaoning@grcbank.com</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>大模型应用、人力外包</t>
+          <t>金融市场/资金/同业、数据服务、风控合规</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>广州农商行官网</t>
+          <t>广州农商银行官网</t>
         </is>
       </c>
     </row>
@@ -3799,55 +3799,185 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>南粤银行</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行新国际结算系统建设项目</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行新国际结算系统建设，预算260万元。要求投标人具有2021年1月1日以来独立承建国内商业银行（资产规模≥3000亿元）总行级别国际结算系统成功案例。</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>260万元</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 10:00</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>陈先生(招标人) 020-28870611; 潘工/祝工(代理) 020-87543323 3271382737@qq.com</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>金融市场/资金/同业、渠道系统</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>👀 ★☆☆ 可关注</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>广州农商</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2026-2028年大模型协同计算平台人月外包开发服务</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>为大模型协同计算平台HiAgent大模型智能体、智能数据洞察大模型、大模型方舟平台等产品的定制化开发，以及报告生成、知识库问答、智能问数及ArkClaw数字员工等智能体建设需求，提供人月外包开发服务。</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>92.16万元</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:00</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>潘先生 020-22389241 / panchaoning@grcbank.com</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>大模型应用、人力外包</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>👀 ★☆☆ 可关注</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>广州农商行官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>海南</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>海南农商</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>预期信用损失法实施项目（2026年-2029年）</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>海南农商银行采取竞争性磋商方式确定预期信用损失法实施项目（2026年-2029年）合作单位，采购预算96万元。</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>96万元</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>竞争性磋商</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>肖小姐 13807519128；邮箱：xiaoshudan@hainanbank.com.cn</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>风控合规</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>海南农商银行官网</t>
         </is>
@@ -3864,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4805,57 +4935,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>江苏银行</t>
+          <t>青银理财</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-2027年基金指数和市场情绪数据采购</t>
+          <t>财务管理系统二期项目</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>为满足业务发展的需要，拟采购基金指数和市场情绪数据服务，用于专业投资研究建设。包括但不限于指数专区、FOF专区、全球市场专区、正收益排行榜、定制化投研、超级指标、纯债基金等基金专区等。本项目2026-07-03首次招标，07-13终止后于当日重新发布招标公告。</t>
+          <t>财务管理系统二期建设。邀请采购，受邀供应商为用友金融信息技术股份有限公司，答复截止2026-07-27，07-28竞价。</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 09:00</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>邀请招标</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>李智龙 13952002026；代理机构：江苏省招标中心有限公司 025-83301084</t>
+          <t>青银理财 0532-66723897（青岛阳光采购平台）</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>数据服务、金融市场/资金/同业</t>
+          <t>数据平台</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>☆☆☆ 不建议</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>银行旧关键词</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -4875,27 +5005,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>农行江苏分行</t>
+          <t>江苏银行</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>智能资产配置服务项目</t>
+          <t>2026-2027年基金指数和市场情绪数据采购</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>为进一步加快财富管理业务发展，为基层理财经理及财富顾问提供专业支持，全面提升私行及高价值客户服务效率，拟采购智能资产配置服务。通过引入外部权威数据及模型规则，推动AI赋能智能化配置，提升服务效率和财富管理专业化水平。实施周期3个月，服务期12个月。</t>
+          <t>为满足业务发展的需要，拟采购基金指数和市场情绪数据服务，用于专业投资研究建设。包括但不限于指数专区、FOF专区、全球市场专区、正收益排行榜、定制化投研、超级指标、纯债基金等基金专区等。本项目2026-07-03首次招标，07-13终止后于当日重新发布招标公告。</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>424.5万元（不含税）</t>
+          <t>71万元</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23 09:00</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4905,12 +5035,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>招标编号：JSTCC26005104585；代理机构：江苏省招标中心有限公司</t>
+          <t>李智龙 13952002026；代理机构：江苏省招标中心有限公司 025-83301084</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>财富管理</t>
+          <t>数据服务、金融市场/资金/同业</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4920,7 +5050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>银行旧关键词</t>
         </is>
       </c>
     </row>
@@ -4940,27 +5070,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>苏州农商</t>
+          <t>农行江苏分行</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（人工智能）</t>
+          <t>智能资产配置服务项目</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>江苏苏州农商行数据类通用技术外包服务项目（人工智能方向），框架入围不超过10家供应商，协议期限3年。</t>
+          <t>为进一步加快财富管理业务发展，为基层理财经理及财富顾问提供专业支持，全面提升私行及高价值客户服务效率，拟采购智能资产配置服务。通过引入外部权威数据及模型规则，推动AI赋能智能化配置，提升服务效率和财富管理专业化水平。实施周期3个月，服务期12个月。</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>框架入围（无固定总预算）</t>
+          <t>424.5万元（不含税）</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:00</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4970,22 +5100,22 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785；标书寄送地址：苏州市吴江区东太湖大道10888号（苏州农商银行综合大楼一楼收发室集采专用）</t>
+          <t>招标编号：JSTCC26005104585；代理机构：江苏省招标中心有限公司</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>人力外包、大模型应用</t>
+          <t>财富管理</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 已截止</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>苏州农商银行采购管理平台</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -5010,17 +5140,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（应用开发）</t>
+          <t>2026年度数据类通用技术外包服务项目（人工智能）</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行数据类通用技术外包服务采购，提供应用开发技术外包服务，框架协议形式，入围供应商不超过15家，协议期限3年。</t>
+          <t>江苏苏州农商行数据类通用技术外包服务项目（人工智能方向），框架入围不超过10家供应商，协议期限3年。</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>框架待查</t>
+          <t>框架入围（无固定总预算）</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -5035,12 +5165,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785；苏州市吴江区东太湖大道10888号苏州农商银行综合大楼一楼收发室集采专用</t>
+          <t>钱女士 0512-63969785；标书寄送地址：苏州市吴江区东太湖大道10888号（苏州农商银行综合大楼一楼收发室集采专用）</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>数据平台、人力外包</t>
+          <t>人力外包、大模型应用</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5050,7 +5180,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行官网</t>
+          <t>苏州农商银行采购管理平台</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5205,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026年度数据类通用技术外包服务项目（数据分析）</t>
+          <t>2026年度数据类通用技术外包服务项目（应用开发）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>苏州农商行数据类通用技术外包服务采购，提供数据分析技术外包服务，框架协议形式，入围供应商不超过10家，协议期限3年。</t>
+          <t>苏州农商行数据类通用技术外包服务采购，提供应用开发技术外包服务，框架协议形式，入围供应商不超过15家，协议期限3年。</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5105,7 +5235,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>数据服务、人力外包</t>
+          <t>数据平台、人力外包</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5140,22 +5270,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>数据类通用技术外包服务采购（数据开发）</t>
+          <t>2026年度数据类通用技术外包服务项目（数据分析）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>采购数据开发类通用技术外包服务，入围供应商不超过15家，签订3年期数据开发类通用技术外包框架合同。</t>
+          <t>苏州农商行数据类通用技术外包服务采购，提供数据分析技术外包服务，框架协议形式，入围供应商不超过10家，协议期限3年。</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>框架待查</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 23:59</t>
+          <t>2026-07-16 16:00</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5165,12 +5295,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>钱女士 0512-63969785（入围15家，3年框架）</t>
+          <t>钱女士 0512-63969785；苏州市吴江区东太湖大道10888号苏州农商银行综合大楼一楼收发室集采专用</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>数据平台、人力外包</t>
+          <t>数据服务、人力外包</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5180,7 +5310,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>苏州农商银行采购管理平台</t>
+          <t>苏州农商行官网</t>
         </is>
       </c>
     </row>
@@ -5195,22 +5325,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>浙商银行</t>
+          <t>苏州农商</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>国产化资产托管系统建设及个性化功能迁移改造项目</t>
+          <t>数据类通用技术外包服务采购（数据开发）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>国产化资产托管系统建设及个性化功能迁移改造，需通过POC测试。竞争性磋商。磋商保证金：10万元。</t>
+          <t>采购数据开发类通用技术外包服务，入围供应商不超过15家，签订3年期数据开发类通用技术外包框架合同。</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5220,32 +5350,32 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 09:00</t>
+          <t>2026-07-16 23:59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>竞争性磋商</t>
+          <t>公开招标</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>季老师 0571-88260758；POC测试联系人：程老师 0571-****1279</t>
+          <t>钱女士 0512-63969785（入围15家，3年框架）</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>信创/国产化、资产托管</t>
+          <t>数据平台、人力外包</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>☆☆☆ 已截止</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>苏州农商银行采购管理平台</t>
         </is>
       </c>
     </row>
@@ -5260,52 +5390,52 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>浙商银行</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>国产化资产托管系统建设及个性化功能迁移改造项目</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>国产化资产托管系统建设及个性化功能迁移改造，需通过POC测试。竞争性磋商。磋商保证金：10万元。</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-07-24 09:00</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>公开招标</t>
+          <t>竞争性磋商</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>季老师 0571-88260758；POC测试联系人：程老师 0571-****1279</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>信创/国产化、资产托管</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5335,12 +5465,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5350,7 +5480,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5360,17 +5490,17 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5390,32 +5520,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>兴银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>理财登记过户（TA）系统产品优化项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>145.89万元</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:30</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5425,22 +5555,22 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -5450,27 +5580,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
+          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5480,7 +5610,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -5490,22 +5620,22 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>移动支付网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -5515,37 +5645,37 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴银理财</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+          <t>理财登记过户（TA）系统产品优化项目</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>145.89万元</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-08-07 09:30</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5555,12 +5685,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5570,7 +5700,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5725,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5610,7 +5740,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-31 09:30</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -5620,7 +5750,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -5635,7 +5765,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>移动支付网</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5780,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>湖南银行</t>
+          <t>中原银行</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026年数字人民币系统研发项目</t>
+          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>60万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 10:00</t>
+          <t>2026-07-31 14:30</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -5685,22 +5815,22 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>渠道系统、信创/国产化</t>
+          <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>湖南银行官网</t>
+          <t>电力招标采购网</t>
         </is>
       </c>
     </row>
@@ -5715,32 +5845,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>湖南银行</t>
+          <t>中原银行</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>客户经理工作台（投顾版）建设项目</t>
+          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>220万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 23:59</t>
+          <t>2026-07-31 14:30</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -5750,22 +5880,22 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
+          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>财富管理、渠道系统</t>
+          <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>湖南招标网</t>
+          <t>电力招标采购网</t>
         </is>
       </c>
     </row>
@@ -5775,37 +5905,37 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>四川农商联合银行</t>
+          <t>湖南银行</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>大模型基础平台及业务创新场景研发项目-智能算力资源采购</t>
+          <t>2026年数字人民币系统研发项目</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>采购智能算力服务器资源，用于大模型平台项目开发测试环境。</t>
+          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>439.2万元</t>
+          <t>60万元</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 11:00</t>
+          <t>2026-07-22 10:00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -5815,22 +5945,22 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>028-85357015</t>
+          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>渠道系统、信创/国产化</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>湖南银行官网</t>
         </is>
       </c>
     </row>
@@ -5840,37 +5970,37 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>贵州农商联合银行</t>
+          <t>湖南银行</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>IT资产设备统一技术选型（国产PC终端、国产黑白A4打印机）</t>
+          <t>客户经理工作台（投顾版）建设项目</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>国产PC终端、国产黑白A4打印机技术选型</t>
+          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>220万元</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23 23:59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -5880,22 +6010,22 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>陈老师(业务)/代老师(招标) 18748826330/0851-82592720; 潘瑞/桂刚/钱大鹏/刘岳(代理) 0851-84812466</t>
+          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>信创/国产化</t>
+          <t>财富管理、渠道系统</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>贵州农商联合银行</t>
+          <t>湖南招标网</t>
         </is>
       </c>
     </row>
@@ -5910,32 +6040,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>建行云南分行</t>
+          <t>四川农商联合银行</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>云南省2026至2027年度信息技术开发服务</t>
+          <t>大模型基础平台及业务创新场景研发项目-智能算力资源采购</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>云南建行特色业务应用系统研发，涵盖财政、社保、医保、ETC、资金监管、个人金融等业务系统的迭代优化、云原生及信创改造，提供软件开发技术人力服务。入选3家，配额5:3:2。</t>
+          <t>采购智能算力服务器资源，用于大模型平台项目开发测试环境。</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1237.2万元</t>
+          <t>439.2万元</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 09:30</t>
+          <t>2026-07-21 11:00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -5945,22 +6075,22 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>李老师 0871-63063106 / 0871-63063110；代理机构：杨倩 15911660979 / 340551535@qq.com</t>
+          <t>028-85357015</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>人力外包、信创/国产化</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>☆☆☆ 已截止</t>
+          <t>👀 ★☆☆ 可关注</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>建设银行龙集采平台</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -5970,37 +6100,37 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>广州农商</t>
+          <t>贵州农商联合银行</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>同业客户信息数据服务项目</t>
+          <t>IT资产设备统一技术选型（国产PC终端、国产黑白A4打印机）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>采购同业客户信息数据服务，包括监管报送数据（含同业客户基本信息）及风控数据（含诚信档案、司法诉讼、同业机构新闻舆情数据）等，项目限价118万元，采购有效期2年。</t>
+          <t>国产PC终端、国产黑白A4打印机技术选型</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>118万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 9:00</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -6010,12 +6140,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>潘先生 020-22389241 / 邮箱 panchaoning@grcbank.com</t>
+          <t>陈老师(业务)/代老师(招标) 18748826330/0851-82592720; 潘瑞/桂刚/钱大鹏/刘岳(代理) 0851-84812466</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、数据服务、风控合规</t>
+          <t>信创/国产化</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -6025,7 +6155,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>广州农商银行官网</t>
+          <t>贵州农商联合银行</t>
         </is>
       </c>
     </row>
@@ -6035,37 +6165,37 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>南粤银行</t>
+          <t>建行云南分行</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行新国际结算系统建设项目</t>
+          <t>云南省2026至2027年度信息技术开发服务</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行新国际结算系统建设，预算260万元。要求投标人具有2021年1月1日以来独立承建国内商业银行（资产规模≥3000亿元）总行级别国际结算系统成功案例。</t>
+          <t>云南建行特色业务应用系统研发，涵盖财政、社保、医保、ETC、资金监管、个人金融等业务系统的迭代优化、云原生及信创改造，提供软件开发技术人力服务。入选3家，配额5:3:2。</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>260万元</t>
+          <t>1237.2万元</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 10:00</t>
+          <t>2026-07-16 09:30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -6075,22 +6205,22 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>陈先生(招标人) 020-28870611; 潘工/祝工(代理) 020-87543323 3271382737@qq.com</t>
+          <t>李老师 0871-63063106 / 0871-63063110；代理机构：杨倩 15911660979 / 340551535@qq.com</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、渠道系统</t>
+          <t>人力外包、信创/国产化</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>👀 ★☆☆ 可关注</t>
+          <t>☆☆☆ 已截止</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>广东南粤银行官网</t>
+          <t>建设银行龙集采平台</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6245,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-2028年大模型协同计算平台人月外包开发服务</t>
+          <t>同业客户信息数据服务项目</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>为大模型协同计算平台HiAgent大模型智能体、智能数据洞察大模型、大模型方舟平台等产品的定制化开发，以及报告生成、知识库问答、智能问数及ArkClaw数字员工等智能体建设需求，提供人月外包开发服务。</t>
+          <t>采购同业客户信息数据服务，包括监管报送数据（含同业客户基本信息）及风控数据（含诚信档案、司法诉讼、同业机构新闻舆情数据）等，项目限价118万元，采购有效期2年。</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>92.16万元</t>
+          <t>118万元</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 09:00</t>
+          <t>2026-07-30 9:00</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -6140,12 +6270,12 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>潘先生 020-22389241 / panchaoning@grcbank.com</t>
+          <t>潘先生 020-22389241 / 邮箱 panchaoning@grcbank.com</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>大模型应用、人力外包</t>
+          <t>金融市场/资金/同业、数据服务、风控合规</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -6155,7 +6285,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>广州农商行官网</t>
+          <t>广州农商银行官网</t>
         </is>
       </c>
     </row>
@@ -6170,55 +6300,185 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>南粤银行</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行新国际结算系统建设项目</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行新国际结算系统建设，预算260万元。要求投标人具有2021年1月1日以来独立承建国内商业银行（资产规模≥3000亿元）总行级别国际结算系统成功案例。</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>260万元</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 10:00</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>陈先生(招标人) 020-28870611; 潘工/祝工(代理) 020-87543323 3271382737@qq.com</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>金融市场/资金/同业、渠道系统</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>👀 ★☆☆ 可关注</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>广东南粤银行官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>广州农商</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-2028年大模型协同计算平台人月外包开发服务</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>为大模型协同计算平台HiAgent大模型智能体、智能数据洞察大模型、大模型方舟平台等产品的定制化开发，以及报告生成、知识库问答、智能问数及ArkClaw数字员工等智能体建设需求，提供人月外包开发服务。</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>92.16万元</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:00</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>潘先生 020-22389241 / panchaoning@grcbank.com</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>大模型应用、人力外包</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>👀 ★☆☆ 可关注</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>广州农商行官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>海南</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>海南农商</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>预期信用损失法实施项目（2026年-2029年）</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>海南农商银行采取竞争性磋商方式确定预期信用损失法实施项目（2026年-2029年）合作单位，采购预算96万元。</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>96万元</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>竞争性磋商</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>肖小姐 13807519128；邮箱：xiaoshudan@hainanbank.com.cn</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>风控合规</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>海南农商银行官网</t>
         </is>
@@ -7371,7 +7631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7792,32 +8052,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>兴银理财</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>理财登记过户（TA）系统产品优化项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>145.89万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7827,7 +8087,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -7852,37 +8112,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴银理财</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
+          <t>理财登记过户（TA）系统产品优化项目</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
+          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>145.89万元</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:30</t>
+          <t>2026-08-07 09:30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7892,12 +8152,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
+          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7907,7 +8167,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>移动支付网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -7932,12 +8192,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7947,7 +8207,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-31 09:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7957,7 +8217,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -7972,7 +8232,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>移动支付网</t>
         </is>
       </c>
     </row>
@@ -7997,45 +8257,110 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:30</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>金融市场/资金/同业、风控合规</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>🔥 ★★★ 强烈建议投标</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>电力招标采购网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>中原银行</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-07-31 14:30</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>公开招标</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>电力招标采购网</t>
         </is>
@@ -8052,7 +8377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8998,27 +9323,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -9028,22 +9353,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -9063,27 +9388,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>徽银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -9093,12 +9418,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9108,7 +9433,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -9123,32 +9448,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>兴银理财</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>理财登记过户（TA）系统产品优化项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
+          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>145.89万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9158,17 +9483,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -9193,27 +9518,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>兴业信托</t>
+          <t>兴银理财</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026年资管系统数据资讯服务项目</t>
+          <t>理财登记过户（TA）系统产品优化项目</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>采购资管系统数据资讯服务，支持信托资产管理业务的数据需求，预算106万元。</t>
+          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>106万元</t>
+          <t>145.89万元</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27 13:30</t>
+          <t>2026-08-07 09:30</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9223,22 +9548,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>联系方式：19*******37（需登录水滴标讯查看完整联系方式）</t>
+          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据服务</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>水滴标讯</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -9248,37 +9573,37 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴业信托</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
+          <t>2026年资管系统数据资讯服务项目</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
+          <t>采购资管系统数据资讯服务，支持信托资产管理业务的数据需求，预算106万元。</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>106万元</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:30</t>
+          <t>2026-07-27 13:30</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9288,22 +9613,22 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
+          <t>联系方式：19*******37（需登录水滴标讯查看完整联系方式）</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理、数据服务</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>🔥 ★★★ 强烈建议投标</t>
+          <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>移动支付网</t>
+          <t>水滴标讯</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9653,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9343,7 +9668,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-31 09:30</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9353,7 +9678,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -9368,7 +9693,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>移动支付网</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9718,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9418,7 +9743,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -9448,32 +9773,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>湖南银行</t>
+          <t>中原银行</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026年数字人民币系统研发项目</t>
+          <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 10:00</t>
+          <t>2026-07-31 14:30</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9483,22 +9808,22 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
+          <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>渠道系统、信创/国产化</t>
+          <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>湖南银行官网</t>
+          <t>电力招标采购网</t>
         </is>
       </c>
     </row>
@@ -9523,22 +9848,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>客户经理工作台（投顾版）建设项目</t>
+          <t>2026年数字人民币系统研发项目</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
+          <t>湖南银行数字人民币系统研发服务采购，推进数字人民币相关系统开发建设，满足银行数字化转型及数字人民币业务拓展需求。</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>220万元</t>
+          <t>60万元</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 23:59</t>
+          <t>2026-07-22 10:00</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9548,12 +9873,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
+          <t>周女士 0731-89829735；代理机构：杨桃/吴洋/董征/张玉珍 0731-84418163、15243678487</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>财富管理、渠道系统</t>
+          <t>渠道系统、信创/国产化</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9563,7 +9888,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>湖南招标网</t>
+          <t>湖南银行官网</t>
         </is>
       </c>
     </row>
@@ -9573,52 +9898,52 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>华能贵诚信托</t>
+          <t>湖南银行</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>估值系统上交所新竞价新综业改造项目</t>
+          <t>客户经理工作台（投顾版）建设项目</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>恒生估值核算系统上交所新债券竞价、新综合业务平台相关改造。直接采购，拟定供应商为恒生电子股份有限公司，公示期2026-07-16至07-19。</t>
+          <t>建设投顾版客户经理工作台系统，支持银行理财经理投资顾问业务开展，预算220万元。</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>220万元</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-23 23:59</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>单一来源采购</t>
+          <t>公开招标</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>周经理 010-68292029 zhouys@hngtrust.com</t>
+          <t>周经理 0731-89829735；代理机构：杨洋/彭笛/周婷 0731-84515046</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>财富管理、渠道系统</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -9628,7 +9953,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>湖南招标网</t>
         </is>
       </c>
     </row>
@@ -9638,60 +9963,125 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>西南</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>华能贵诚信托</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>估值系统上交所新竞价新综业改造项目</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>恒生估值核算系统上交所新债券竞价、新综合业务平台相关改造。直接采购，拟定供应商为恒生电子股份有限公司，公示期2026-07-16至07-19。</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>单一来源采购</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>周经理 010-68292029 zhouys@hngtrust.com</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>⭐ ★★☆ 建议投标</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>天眼查</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>华南</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>海南</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>海南农商</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>预期信用损失法实施项目（2026年-2029年）</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>海南农商银行采取竞争性磋商方式确定预期信用损失法实施项目（2026年-2029年）合作单位，采购预算96万元。</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>96万元</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>竞争性磋商</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>肖小姐 13807519128；邮箱：xiaoshudan@hainanbank.com.cn</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>风控合规</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>⭐ ★★☆ 建议投标</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>海南农商银行官网</t>
         </is>

--- a/恒生银信招标资讯每日速递_2026年7月17日.xlsx
+++ b/恒生银信招标资讯每日速递_2026年7月17日.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部有效招标（53）" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="银行行业（37）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信托行业（16）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强烈建议投标（10）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强烈建议投标（11）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建议投标（25）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>数据平台</t>
+          <t>资产管理、其他</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>智慧组合管理平台建设项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
+          <t>为承接公司数字化转型蓝图规划，突破公司在专业化投资研究、多资产多策略的组合管理、实时穿透的头寸与流动性管理方面的瓶颈，解决当前系统中投资数据时效性与一致性的问题，拟开展“IBOR底座及头寸管理建设项目”，建设公司统一、精准的投研交易领域的数字底座，为智能化指令排布、模拟试算、实时头寸跟踪等应用功能提供数据支撑，推动公司投研、交易、风控全流程的数字化与智能化升级，详细内容详见本招标文件。</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2599,22 +2599,22 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -2634,27 +2634,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>徽银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>数据平台</t>
+          <t>资产管理、其他</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>智慧组合管理平台建设项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
+          <t>为承接公司数字化转型蓝图规划，突破公司在专业化投资研究、多资产多策略的组合管理、实时穿透的头寸与流动性管理方面的瓶颈，解决当前系统中投资数据时效性与一致性的问题，拟开展“IBOR底座及头寸管理建设项目”，建设公司统一、精准的投研交易领域的数字底座，为智能化指令排布、模拟试算、实时头寸跟踪等应用功能提供数据支撑，推动公司投研、交易、风控全流程的数字化与智能化升级，详细内容详见本招标文件。</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -5525,27 +5525,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5555,22 +5555,22 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -5590,27 +5590,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>徽银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>智慧组合管理平台建设项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
+          <t>为承接公司数字化转型蓝图规划，突破公司在专业化投资研究、多资产多策略的组合管理、实时穿透的头寸与流动性管理方面的瓶颈，解决当前系统中投资数据时效性与一致性的问题，拟开展“IBOR底座及头寸管理建设项目”，建设公司统一、精准的投研交易领域的数字底座，为智能化指令排布、模拟试算、实时头寸跟踪等应用功能提供数据支撑，推动公司投研、交易、风控全流程的数字化与智能化升级，详细内容详见本招标文件。</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -8117,32 +8117,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>兴银理财</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>理财登记过户（TA）系统产品优化项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>145.89万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 09:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -8177,37 +8177,37 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>中原银行</t>
+          <t>兴银理财</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
+          <t>理财登记过户（TA）系统产品优化项目</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
+          <t>对现有理财登记过户（TA）系统进行产品优化升级，最高限价145.89万元（含税），公开招标，地点福州。</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>145.89万元</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 09:30</t>
+          <t>2026-08-07 09:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
+          <t>代理机构：公诚管理咨询有限公司 殷浩楠、陈碧霞、王红兰 18806091031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>金融市场/资金/同业、风控合规</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>移动支付网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -8257,12 +8257,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+          <t>新一代资金交易管理系统项目（资金业务前台交易系统）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+          <t>中原银行新一代资金交易管理系统建设，资金业务前台交易系统部分，支持资金业务交易处理。</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30</t>
+          <t>2026-07-31 09:30</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+          <t>招标人：张先生 0371-85517996 / 代理机构：李菲等 15625090818 / 邮箱 ahszbjt123@163.com</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>电力招标采购网</t>
+          <t>移动支付网</t>
         </is>
       </c>
     </row>
@@ -8322,45 +8322,110 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>新一代资金交易管理系统项目（资金业务中台风控系统）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>中原银行新一代资金交易管理系统建设，资金业务中台风控系统部分，满足资金业务风险管理需求。</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 14:30</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>招标人：张先生 0371-85517996 / 代理机构：万雪桢等 18003717459 / 邮箱 18003717459@189.cn</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>金融市场/资金/同业、风控合规</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>🔥 ★★★ 强烈建议投标</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>电力招标采购网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>中原银行</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>新一代资金交易管理系统（资金业务后台运营管理系统）</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>中原银行新一代资金交易管理系统建设，资金业务后台运营管理系统部分，支持资金业务后台运营。</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-07-31 14:30</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>公开招标</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>公开招标</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>招标人：张先生 0371-85517996 / 平台联系人：李杨 18811547188</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>金融市场/资金/同业、风控合规</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>电力招标采购网</t>
         </is>
@@ -9328,12 +9393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>智慧组合管理平台建设项目</t>
+          <t>IBOR底座及头寸管理建设项目</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
+          <t>为承接公司数字化转型蓝图规划，突破公司在专业化投资研究、多资产多策略的组合管理、实时穿透的头寸与流动性管理方面的瓶颈，解决当前系统中投资数据时效性与一致性的问题，拟开展“IBOR底座及头寸管理建设项目”，建设公司统一、精准的投研交易领域的数字底座，为智能化指令排布、模拟试算、实时头寸跟踪等应用功能提供数据支撑，推动公司投研、交易、风控全流程的数字化与智能化升级，详细内容详见本招标文件。</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9343,7 +9408,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 14:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -9353,12 +9418,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
+          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>资产管理、数据平台</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -9388,27 +9453,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>徽商银行</t>
+          <t>徽银理财</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>智能分析平台建设采购项目</t>
+          <t>智慧组合管理平台建设项目</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
+          <t>为承接公司数字化转型蓝图规划，解决当前投资管理中存在的数据割裂、决策延迟、流程手工化、分析工具缺失等痛点，对标国内外同业先进实践，启动智慧组合管理平台建设，通过系统化、自动化、智能化方式赋能投前、投中、投后全流程，优化模拟试算、交易排布和组合分析流程，逐步实现由平台驱动、数据赋能的现代化投资管理模式转型。</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>420万元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 14:30</t>
+          <t>2026-08-04 14:30</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -9418,22 +9483,22 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>徐工 0551-62586899</t>
+          <t>董经理 0551-65199018、18156091788；招标代理：安徽中技工程咨询有限公司 王思远、张睿 18226380158、18225519675</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>大模型应用</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>⭐ ★★☆ 建议投标</t>
+          <t>🔥 ★★★ 强烈建议投标</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>千里马招标网</t>
+          <t>天眼查</t>
         </is>
       </c>
     </row>
@@ -9453,27 +9518,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>徽银理财</t>
+          <t>徽商银行</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>IBOR底座及头寸管理建设项目</t>
+          <t>智能分析平台建设采购项目</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>建设IBOR（实时持仓簿记）数据底座及头寸管理能力，支撑资管一体化平台。2026-07-14发布于安徽省招标投标信息网。</t>
+          <t>基于行内湖仓一体数据架构建设统一报表数据底座，搭建指标管理平台并统一报表指标库，打造统一数据门户，采购统一报表开发工具，重构自助分析区，完成业务智能分析云平台报表迁移，支撑全行数智化转型。</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420万元</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21 14:30</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9483,12 +9548,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>徽银理财 0551-65199001（天眼查工商信息，2025年年报）</t>
+          <t>徐工 0551-62586899</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>资产管理、数据平台</t>
+          <t>大模型应用</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -9498,7 +9563,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>天眼查</t>
+          <t>千里马招标网</t>
         </is>
       </c>
     </row>
